--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_4_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_4_bus.xlsx
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.019485521667468</v>
+        <v>1.019485521667526</v>
       </c>
       <c r="G2">
-        <v>149.9612089037749</v>
+        <v>-0.03879109617642165</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8902319386642066</v>
+        <v>0.8902319386646702</v>
       </c>
       <c r="G3">
-        <v>149.220203107533</v>
+        <v>-0.7797968923376495</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.84533394365662</v>
+        <v>0.8453339436572476</v>
       </c>
       <c r="G4">
-        <v>151.2672005251284</v>
+        <v>1.26720052526844</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8453339436712278</v>
+        <v>0.8453339436718403</v>
       </c>
       <c r="G5">
-        <v>1.267200529701654</v>
+        <v>1.267200529835319</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -618,22 +618,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.05035537883598</v>
+        <v>40.05035537881115</v>
       </c>
       <c r="C6">
-        <v>27.7477005644063</v>
+        <v>27.74770056438911</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100661764</v>
+        <v>0.0007385329100534613</v>
       </c>
       <c r="E6">
-        <v>0.00600934383484958</v>
+        <v>0.006009343834854925</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>82.99362924199868</v>
+        <v>82.99362924212427</v>
       </c>
     </row>
   </sheetData>
@@ -746,22 +746,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023840732</v>
+        <v>1.092677014703385</v>
       </c>
       <c r="O2">
-        <v>1.077288329849863</v>
+        <v>1.069211965323062</v>
       </c>
       <c r="P2">
-        <v>1.07669458101103</v>
+        <v>1.092091632423271</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999588</v>
+        <v>29.29211872291256</v>
       </c>
       <c r="R2">
-        <v>59.26415434316668</v>
+        <v>-90.03597083799249</v>
       </c>
       <c r="S2">
-        <v>-59.31733392295215</v>
+        <v>150.6906508046328</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023839415</v>
+        <v>1.067403369962787</v>
       </c>
       <c r="O3">
-        <v>0.9874262514306115</v>
+        <v>0.938787168673215</v>
       </c>
       <c r="P3">
-        <v>0.9756902409599142</v>
+        <v>1.056556102863581</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999191</v>
+        <v>26.08578028765334</v>
       </c>
       <c r="R3">
-        <v>55.4163150933915</v>
+        <v>-90.73804141973433</v>
       </c>
       <c r="S3">
-        <v>-56.42897641831742</v>
+        <v>153.6258712173467</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023839416</v>
+        <v>1.043533396801504</v>
       </c>
       <c r="O4">
-        <v>0.9397573987310375</v>
+        <v>0.8935122209079079</v>
       </c>
       <c r="P4">
-        <v>0.958854624600889</v>
+        <v>1.060763957197483</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999191</v>
+        <v>25.34206720922742</v>
       </c>
       <c r="R4">
-        <v>55.40861810179866</v>
+        <v>-88.77958323307151</v>
       </c>
       <c r="S4">
-        <v>-53.78696291872183</v>
+        <v>155.0979067334727</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.043533396771213</v>
+        <v>1.043533396772156</v>
       </c>
       <c r="O5">
-        <v>0.893512220922287</v>
+        <v>0.8935122209233323</v>
       </c>
       <c r="P5">
-        <v>1.060763957231744</v>
+        <v>1.060763957232851</v>
       </c>
       <c r="Q5">
-        <v>25.34206721033249</v>
+        <v>25.34206721041291</v>
       </c>
       <c r="R5">
-        <v>-88.77958322858819</v>
+        <v>-88.77958322850462</v>
       </c>
       <c r="S5">
-        <v>155.0979067338755</v>
+        <v>155.0979067339455</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -949,55 +949,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.99498474368647</v>
+        <v>34.99498474368728</v>
       </c>
       <c r="D6">
-        <v>34.99498474368647</v>
+        <v>34.99498474368728</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.081745665249086</v>
+        <v>8.081745665249272</v>
       </c>
       <c r="G6">
-        <v>8.081745665249086</v>
+        <v>8.081745665249272</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
-        <v>0.9526279648085261</v>
+        <v>0.9526279648080223</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648087453</v>
+        <v>0.9526279648083096</v>
       </c>
       <c r="Q6">
-        <v>-2.171229709496621E-11</v>
+        <v>-1.133107196134247E-11</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999598</v>
+        <v>-179.9999999999827</v>
       </c>
     </row>
   </sheetData>
@@ -1110,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952316283</v>
+        <v>1.050004138519517</v>
       </c>
       <c r="O2">
-        <v>1.049983921824036</v>
+        <v>1.049959518374844</v>
       </c>
       <c r="P2">
-        <v>1.049955331993707</v>
+        <v>1.04997554923967</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999927</v>
+        <v>29.99859426342729</v>
       </c>
       <c r="R2">
-        <v>59.99769354003367</v>
+        <v>-90.00180143451601</v>
       </c>
       <c r="S2">
-        <v>-60.00039563978348</v>
+        <v>150.0005050713337</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1169,22 +1169,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952316282</v>
+        <v>1.050029087220758</v>
       </c>
       <c r="O3">
-        <v>1.049927663576825</v>
+        <v>1.049797089600016</v>
       </c>
       <c r="P3">
-        <v>1.049767948256756</v>
+        <v>1.049869387330141</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999926</v>
+        <v>29.99269099044333</v>
       </c>
       <c r="R3">
-        <v>59.98765891417082</v>
+        <v>-90.01006399193564</v>
       </c>
       <c r="S3">
-        <v>-60.00275344354486</v>
+        <v>150.0022784719106</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1228,22 +1228,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952316282</v>
+        <v>1.050008313510064</v>
       </c>
       <c r="O4">
-        <v>1.049860334070204</v>
+        <v>1.049703970218128</v>
       </c>
       <c r="P4">
-        <v>1.049695606600145</v>
+        <v>1.049843609258967</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999926</v>
+        <v>29.99041181059042</v>
       </c>
       <c r="R4">
-        <v>59.98522120795439</v>
+        <v>-90.0103800481253</v>
       </c>
       <c r="S4">
-        <v>-60.00078908506565</v>
+        <v>150.0044003598865</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.050008313510004</v>
+        <v>1.050008313510005</v>
       </c>
       <c r="O5">
         <v>1.049703970218074</v>
       </c>
       <c r="P5">
-        <v>1.049843609258998</v>
+        <v>1.049843609258999</v>
       </c>
       <c r="Q5">
-        <v>29.9904118105905</v>
+        <v>29.99041181059059</v>
       </c>
       <c r="R5">
-        <v>-90.01038004811966</v>
+        <v>-90.01038004811957</v>
       </c>
       <c r="S5">
-        <v>150.0044003598891</v>
+        <v>150.0044003598892</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1313,55 +1313,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.05931688229148749</v>
+        <v>0.05931688229148746</v>
       </c>
       <c r="D6">
-        <v>0.0593168822914875</v>
+        <v>0.05931688229148747</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.01369864738751761</v>
+        <v>0.0136986473875176</v>
       </c>
       <c r="G6">
         <v>0.01369864738751761</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>1.050124249534621</v>
+        <v>1.05012424953462</v>
       </c>
       <c r="O6">
-        <v>1.048584227053752</v>
+        <v>1.048584227053751</v>
       </c>
       <c r="P6">
         <v>1.049167932672647</v>
       </c>
       <c r="Q6">
-        <v>29.95148164044748</v>
+        <v>29.95148164044761</v>
       </c>
       <c r="R6">
-        <v>-90.06031761863291</v>
+        <v>-90.06031761863277</v>
       </c>
       <c r="S6">
-        <v>150.0184205536894</v>
+        <v>150.0184205536895</v>
       </c>
     </row>
   </sheetData>
@@ -1474,22 +1474,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023841856</v>
+        <v>1.100004408047329</v>
       </c>
       <c r="O2">
-        <v>1.099983229010162</v>
+        <v>1.099957665190901</v>
       </c>
       <c r="P2">
-        <v>1.09995328079912</v>
+        <v>1.099974460412913</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999927</v>
+        <v>29.99859432538236</v>
       </c>
       <c r="R2">
-        <v>59.99769369346199</v>
+        <v>-90.00180125156575</v>
       </c>
       <c r="S2">
-        <v>-60.00039551879259</v>
+        <v>150.0005051008476</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1533,22 +1533,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023841855</v>
+        <v>1.100030538759422</v>
       </c>
       <c r="O3">
-        <v>1.099924286805658</v>
+        <v>1.09978750377301</v>
       </c>
       <c r="P3">
-        <v>1.09975698211196</v>
+        <v>1.099863250228143</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999926</v>
+        <v>29.99269129588951</v>
       </c>
       <c r="R3">
-        <v>59.98765970462194</v>
+        <v>-90.01006302180251</v>
       </c>
       <c r="S3">
-        <v>-60.00275277895603</v>
+        <v>150.0022786513712</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1592,22 +1592,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023841855</v>
+        <v>1.100008775115284</v>
       </c>
       <c r="O4">
-        <v>1.0998537527713</v>
+        <v>1.099689954833206</v>
       </c>
       <c r="P4">
-        <v>1.099681201022603</v>
+        <v>1.099836247687822</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999926</v>
+        <v>29.99041227879354</v>
       </c>
       <c r="R4">
-        <v>59.98522227455</v>
+        <v>-90.01037885124781</v>
       </c>
       <c r="S4">
-        <v>-60.0007883566512</v>
+        <v>150.004400489816</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.100008775115218</v>
+        <v>1.100008775115219</v>
       </c>
       <c r="O5">
-        <v>1.099689954833147</v>
+        <v>1.099689954833148</v>
       </c>
       <c r="P5">
-        <v>1.099836247687856</v>
+        <v>1.099836247687857</v>
       </c>
       <c r="Q5">
-        <v>29.99041227879363</v>
+        <v>29.99041227879372</v>
       </c>
       <c r="R5">
-        <v>-90.0103788512419</v>
+        <v>-90.01037885124181</v>
       </c>
       <c r="S5">
-        <v>150.0044004898187</v>
+        <v>150.0044004898188</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1677,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.06213834275095777</v>
+        <v>0.06213834275095775</v>
       </c>
       <c r="D6">
-        <v>0.0621383427509578</v>
+        <v>0.06213834275095776</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1689,43 +1689,43 @@
         <v>0.01435023577954025</v>
       </c>
       <c r="G6">
-        <v>0.01435023577954026</v>
+        <v>0.01435023577954025</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
-        <v>1.100135989306264</v>
+        <v>1.100135989306258</v>
       </c>
       <c r="O6">
-        <v>1.098461071904061</v>
+        <v>1.098461071904055</v>
       </c>
       <c r="P6">
-        <v>1.099094739754298</v>
+        <v>1.099094739754291</v>
       </c>
       <c r="Q6">
-        <v>29.9496303018916</v>
+        <v>29.94963030189167</v>
       </c>
       <c r="R6">
-        <v>-90.06269174365455</v>
+        <v>-90.0626917436545</v>
       </c>
       <c r="S6">
-        <v>150.0190896171589</v>
+        <v>150.019089617159</v>
       </c>
     </row>
   </sheetData>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880799651</v>
+        <v>0.9433071223203854</v>
       </c>
       <c r="O2">
-        <v>0.928424086480038</v>
+        <v>0.9202097000245562</v>
       </c>
       <c r="P2">
-        <v>0.9270693298512457</v>
+        <v>0.9419737708741619</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999616</v>
+        <v>29.19323166508389</v>
       </c>
       <c r="R2">
-        <v>59.13315358543498</v>
+        <v>-90.09512014424604</v>
       </c>
       <c r="S2">
-        <v>-59.27352490959455</v>
+        <v>150.7614448346815</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1897,22 +1897,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880798641</v>
+        <v>0.9229023361557279</v>
       </c>
       <c r="O3">
-        <v>0.8519274965736479</v>
+        <v>0.8065751372451115</v>
       </c>
       <c r="P3">
-        <v>0.8374453458536779</v>
+        <v>0.909550971609259</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999652</v>
+        <v>25.90646318835902</v>
       </c>
       <c r="R3">
-        <v>55.06309855496524</v>
+        <v>-91.05627438105914</v>
       </c>
       <c r="S3">
-        <v>-56.5076937503822</v>
+        <v>153.6843148702754</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1956,22 +1956,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999880798649</v>
+        <v>0.889274118221583</v>
       </c>
       <c r="O4">
-        <v>0.7944503111020088</v>
+        <v>0.7636659323889832</v>
       </c>
       <c r="P4">
-        <v>0.833592932014489</v>
+        <v>0.9244102643486043</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999652</v>
+        <v>25.39291889705171</v>
       </c>
       <c r="R4">
-        <v>56.24244369409644</v>
+        <v>-87.09305266723106</v>
       </c>
       <c r="S4">
-        <v>-52.40631232427337</v>
+        <v>155.6364982897638</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8892741181974101</v>
+        <v>0.8892741181968875</v>
       </c>
       <c r="O5">
-        <v>0.7636659324129887</v>
+        <v>0.7636659324123729</v>
       </c>
       <c r="P5">
-        <v>0.9244102643826115</v>
+        <v>0.9244102643820225</v>
       </c>
       <c r="Q5">
-        <v>25.39291889855955</v>
+        <v>25.39291889852582</v>
       </c>
       <c r="R5">
-        <v>-87.09305266246294</v>
+        <v>-87.09305266249409</v>
       </c>
       <c r="S5">
-        <v>155.6364982900396</v>
+        <v>155.636498290016</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2041,55 +2041,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>29.83070070817582</v>
+        <v>29.83070070818455</v>
       </c>
       <c r="D6">
-        <v>29.83070070817582</v>
+        <v>29.83070070818455</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.889105336247854</v>
+        <v>6.889105336249872</v>
       </c>
       <c r="G6">
-        <v>6.889105336247854</v>
+        <v>6.889105336249872</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.8227241232722073</v>
+        <v>0.8227241232723406</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8227241232722783</v>
+        <v>0.822724123272223</v>
       </c>
       <c r="Q6">
-        <v>2.908891997554147E-11</v>
+        <v>9.124841554268777E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999876</v>
+        <v>179.9999999999822</v>
       </c>
     </row>
   </sheetData>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761589889</v>
+        <v>0.8936593665804233</v>
       </c>
       <c r="O2">
-        <v>0.8795596486124707</v>
+        <v>0.8717775983947266</v>
       </c>
       <c r="P2">
-        <v>0.8782761949820358</v>
+        <v>0.8923961915437183</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999616</v>
+        <v>29.19323166508389</v>
       </c>
       <c r="R2">
-        <v>59.13315358543498</v>
+        <v>-90.09512014424604</v>
       </c>
       <c r="S2">
-        <v>-59.27352490959455</v>
+        <v>150.7614448346815</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2261,22 +2261,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761588933</v>
+        <v>0.8743285167992177</v>
       </c>
       <c r="O3">
-        <v>0.8070891960273704</v>
+        <v>0.7641238035783328</v>
       </c>
       <c r="P3">
-        <v>0.7933692639576375</v>
+        <v>0.8616798558262868</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999652</v>
+        <v>25.90646318835902</v>
       </c>
       <c r="R3">
-        <v>55.06309855496525</v>
+        <v>-91.05627438105914</v>
       </c>
       <c r="S3">
-        <v>-56.5076937503822</v>
+        <v>153.6843148702754</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2320,22 +2320,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.899999976158894</v>
+        <v>0.842470205516321</v>
       </c>
       <c r="O4">
-        <v>0.7526371263397582</v>
+        <v>0.723472978491937</v>
       </c>
       <c r="P4">
-        <v>0.7897196087924498</v>
+        <v>0.8757570803304457</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999652</v>
+        <v>25.39291889705171</v>
       </c>
       <c r="R4">
-        <v>56.24244369409644</v>
+        <v>-87.09305266723106</v>
       </c>
       <c r="S4">
-        <v>-52.40631232427338</v>
+        <v>155.6364982897638</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8424702054934203</v>
+        <v>0.8424702054929254</v>
       </c>
       <c r="O5">
-        <v>0.7234729785146793</v>
+        <v>0.7234729785140956</v>
       </c>
       <c r="P5">
-        <v>0.8757570803626631</v>
+        <v>0.8757570803621053</v>
       </c>
       <c r="Q5">
-        <v>25.39291889855955</v>
+        <v>25.39291889852582</v>
       </c>
       <c r="R5">
-        <v>-87.09305266246295</v>
+        <v>-87.09305266249407</v>
       </c>
       <c r="S5">
-        <v>155.6364982900396</v>
+        <v>155.636498290016</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2405,55 +2405,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>28.26066343477081</v>
+        <v>28.26066343477908</v>
       </c>
       <c r="D6">
-        <v>28.26066343477081</v>
+        <v>28.26066343477908</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.526520753869672</v>
+        <v>6.526520753871583</v>
       </c>
       <c r="G6">
-        <v>6.526520753869672</v>
+        <v>6.526520753871583</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.779422842759115</v>
+        <v>0.7794228427592413</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7794228427591822</v>
+        <v>0.7794228427591299</v>
       </c>
       <c r="Q6">
-        <v>2.910916811951608E-11</v>
+        <v>9.14332377144588E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999876</v>
+        <v>179.9999999999822</v>
       </c>
     </row>
   </sheetData>
@@ -2566,22 +2566,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880790736</v>
+        <v>0.9500042913249497</v>
       </c>
       <c r="O2">
-        <v>0.9499835077079177</v>
+        <v>0.9499584202019976</v>
       </c>
       <c r="P2">
-        <v>0.9499541167483274</v>
+        <v>0.949974901008377</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999926</v>
+        <v>29.99840273103079</v>
       </c>
       <c r="R2">
-        <v>59.99737929598991</v>
+        <v>-90.00204685423932</v>
       </c>
       <c r="S2">
-        <v>-60.00044951018042</v>
+        <v>150.0005739090118</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2625,22 +2625,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.949999988079075</v>
+        <v>0.9500274430299677</v>
       </c>
       <c r="O3">
-        <v>0.9499312985903284</v>
+        <v>0.9498076839092947</v>
       </c>
       <c r="P3">
-        <v>0.9497802226059053</v>
+        <v>0.9498763823371301</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999926</v>
+        <v>29.99234777609227</v>
       </c>
       <c r="R3">
-        <v>59.98708683730032</v>
+        <v>-90.01052169766037</v>
       </c>
       <c r="S3">
-        <v>-60.00286778612245</v>
+        <v>150.0023929725073</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2684,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999880790748</v>
+        <v>0.9499838462230713</v>
       </c>
       <c r="O4">
-        <v>0.9498274465944998</v>
+        <v>0.9496871683818491</v>
       </c>
       <c r="P4">
-        <v>0.9497033152804076</v>
+        <v>0.9498597353478828</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999926</v>
+        <v>29.98966943394202</v>
       </c>
       <c r="R4">
-        <v>59.98534566695217</v>
+        <v>-90.0086454085385</v>
       </c>
       <c r="S4">
-        <v>-59.99831164399107</v>
+        <v>150.0060099968995</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499838462230125</v>
+        <v>0.9499838462230119</v>
       </c>
       <c r="O5">
-        <v>0.9496871683818104</v>
+        <v>0.94968716838181</v>
       </c>
       <c r="P5">
-        <v>0.9498597353479231</v>
+        <v>0.9498597353479226</v>
       </c>
       <c r="Q5">
-        <v>29.98966943394286</v>
+        <v>29.98966943394272</v>
       </c>
       <c r="R5">
-        <v>-90.00864540853145</v>
+        <v>-90.00864540853158</v>
       </c>
       <c r="S5">
-        <v>150.0060099969024</v>
+        <v>150.0060099969023</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2769,55 +2769,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.05366222753909052</v>
+        <v>0.05366222753909055</v>
       </c>
       <c r="D6">
-        <v>0.05366222753909052</v>
+        <v>0.05366222753909055</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.01239276079067007</v>
+        <v>0.01239276079067008</v>
       </c>
       <c r="G6">
-        <v>0.01239276079067007</v>
+        <v>0.01239276079067008</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9500940258818821</v>
+        <v>0.9500940258818807</v>
       </c>
       <c r="O6">
-        <v>0.9486231105260785</v>
+        <v>0.9486231105260772</v>
       </c>
       <c r="P6">
-        <v>0.9492176836326902</v>
+        <v>0.9492176836326889</v>
       </c>
       <c r="Q6">
-        <v>29.94878109295503</v>
+        <v>29.94878109295495</v>
       </c>
       <c r="R6">
-        <v>-90.06109628202204</v>
+        <v>-90.06109628202213</v>
       </c>
       <c r="S6">
-        <v>150.0207371868646</v>
+        <v>150.0207371868645</v>
       </c>
     </row>
   </sheetData>
@@ -2930,22 +2930,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761581443</v>
+        <v>0.9000040529173385</v>
       </c>
       <c r="O2">
-        <v>0.8999843631751618</v>
+        <v>0.8999605960646216</v>
       </c>
       <c r="P2">
-        <v>0.8999565191085699</v>
+        <v>0.8999762094599211</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999926</v>
+        <v>29.99840273103079</v>
       </c>
       <c r="R2">
-        <v>59.99737929598991</v>
+        <v>-90.00204685423932</v>
       </c>
       <c r="S2">
-        <v>-60.00044951018042</v>
+        <v>150.0005739090118</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2989,22 +2989,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761581458</v>
+        <v>0.9000259861112604</v>
       </c>
       <c r="O3">
-        <v>0.8999349019065565</v>
+        <v>0.8998177932629994</v>
       </c>
       <c r="P3">
-        <v>0.89979177729173</v>
+        <v>0.899882875983199</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999926</v>
+        <v>29.99234777609227</v>
       </c>
       <c r="R3">
-        <v>59.98708683730032</v>
+        <v>-90.01052169766037</v>
       </c>
       <c r="S3">
-        <v>-60.00286778612245</v>
+        <v>150.0023929725073</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -3048,22 +3048,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999761581459</v>
+        <v>0.8999846838737239</v>
       </c>
       <c r="O4">
-        <v>0.8998365158066166</v>
+        <v>0.8997036206596426</v>
       </c>
       <c r="P4">
-        <v>0.8997189177212217</v>
+        <v>0.8998671051515005</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999926</v>
+        <v>29.98966943394202</v>
       </c>
       <c r="R4">
-        <v>59.98534566695217</v>
+        <v>-90.0086454085385</v>
       </c>
       <c r="S4">
-        <v>-59.99831164399106</v>
+        <v>150.0060099968995</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999846838736681</v>
+        <v>0.8999846838736676</v>
       </c>
       <c r="O5">
-        <v>0.899703620659606</v>
+        <v>0.8997036206596056</v>
       </c>
       <c r="P5">
-        <v>0.8998671051515388</v>
+        <v>0.8998671051515381</v>
       </c>
       <c r="Q5">
-        <v>29.98966943394286</v>
+        <v>29.98966943394272</v>
       </c>
       <c r="R5">
-        <v>-90.00864540853145</v>
+        <v>-90.00864540853158</v>
       </c>
       <c r="S5">
-        <v>150.0060099969024</v>
+        <v>150.0060099969023</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3133,55 +3133,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.05083789906506237</v>
+        <v>0.0508378990650624</v>
       </c>
       <c r="D6">
-        <v>0.05083789906506237</v>
+        <v>0.05083789906506239</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.01174051005904674</v>
+        <v>0.01174051005904675</v>
       </c>
       <c r="G6">
-        <v>0.01174051005904674</v>
+        <v>0.01174051005904675</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9000890646016683</v>
+        <v>0.900089064601667</v>
       </c>
       <c r="O6">
-        <v>0.8986955658629675</v>
+        <v>0.8986955658629663</v>
       </c>
       <c r="P6">
-        <v>0.8992588456403251</v>
+        <v>0.8992588456403238</v>
       </c>
       <c r="Q6">
-        <v>29.94878109295503</v>
+        <v>29.94878109295496</v>
       </c>
       <c r="R6">
-        <v>-90.06109628202204</v>
+        <v>-90.06109628202213</v>
       </c>
       <c r="S6">
-        <v>150.0207371868646</v>
+        <v>150.0207371868645</v>
       </c>
     </row>
   </sheetData>
@@ -3297,22 +3297,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.028239522856078</v>
+        <v>1.033566849172132</v>
       </c>
       <c r="O2">
-        <v>1.044448238764796</v>
+        <v>1.049999952317025</v>
       </c>
       <c r="P2">
-        <v>1.044756423536841</v>
+        <v>1.033878277540526</v>
       </c>
       <c r="Q2">
-        <v>179.9802725658265</v>
+        <v>30.50762743639</v>
       </c>
       <c r="R2">
-        <v>60.51204970130743</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>-60.52160682456672</v>
+        <v>149.4630944931811</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3359,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9360030528623202</v>
+        <v>0.9620310662055093</v>
       </c>
       <c r="O3">
-        <v>1.019167731432405</v>
+        <v>1.049999952317295</v>
       </c>
       <c r="P3">
-        <v>1.026205555670789</v>
+        <v>0.9694837543975473</v>
       </c>
       <c r="Q3">
-        <v>179.515480084302</v>
+        <v>32.58805277810444</v>
       </c>
       <c r="R3">
-        <v>62.66558070737329</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>-62.86850607640068</v>
+        <v>146.7292669372774</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.904119945699863</v>
+        <v>0.9495597156068839</v>
       </c>
       <c r="O4">
-        <v>1.021859660290755</v>
+        <v>1.049999952317295</v>
       </c>
       <c r="P4">
-        <v>1.009093217981124</v>
+        <v>0.9358074645722143</v>
       </c>
       <c r="Q4">
-        <v>-179.0964869929413</v>
+        <v>34.46414049302827</v>
       </c>
       <c r="R4">
-        <v>63.74707437759069</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>-63.38900696426268</v>
+        <v>146.7824713477434</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9495597156370522</v>
+        <v>0.9495597156373937</v>
       </c>
       <c r="O5">
-        <v>1.049999952317119</v>
+        <v>1.049999952317295</v>
       </c>
       <c r="P5">
-        <v>0.9358074645561464</v>
+        <v>0.9358074645563353</v>
       </c>
       <c r="Q5">
-        <v>34.46414049484333</v>
+        <v>34.46414049481969</v>
       </c>
       <c r="R5">
-        <v>-89.99999999997021</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>146.7824713501766</v>
+        <v>146.7824713501617</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>42.83552687293334</v>
+        <v>42.83552687290265</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9.892441335795866</v>
+        <v>9.89244133578878</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3527,43 +3527,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.5899709507611558</v>
+        <v>0.5899709507606072</v>
       </c>
       <c r="O6">
-        <v>1.049999952317594</v>
+        <v>1.049999952315576</v>
       </c>
       <c r="P6">
-        <v>0.5826002436997419</v>
+        <v>0.582600243697349</v>
       </c>
       <c r="Q6">
-        <v>63.7470739932885</v>
+        <v>63.74707399339567</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999147</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S6">
-        <v>116.61099333477</v>
+        <v>116.6109933347426</v>
       </c>
       <c r="T6">
-        <v>42.83552687293334</v>
+        <v>42.83552687290265</v>
       </c>
     </row>
   </sheetData>
@@ -3679,22 +3679,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.078100972187809</v>
+        <v>1.083466586624729</v>
       </c>
       <c r="O2">
-        <v>1.09441720447142</v>
+        <v>1.100000023842603</v>
       </c>
       <c r="P2">
-        <v>1.094715449034042</v>
+        <v>1.083767844717217</v>
       </c>
       <c r="Q2">
-        <v>179.9817881320178</v>
+        <v>30.48787214046775</v>
       </c>
       <c r="R2">
-        <v>60.49196093120953</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>-60.50079496762149</v>
+        <v>149.4850874769905</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.985271114370338</v>
+        <v>1.011458899805297</v>
       </c>
       <c r="O3">
-        <v>1.068957224502241</v>
+        <v>1.100000023842874</v>
       </c>
       <c r="P3">
-        <v>1.075969383984319</v>
+        <v>1.018866857568437</v>
       </c>
       <c r="Q3">
-        <v>179.5409262837121</v>
+        <v>32.48031732117402</v>
       </c>
       <c r="R3">
-        <v>62.55858513519847</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>-62.75231025285019</v>
+        <v>146.8710330066728</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3803,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.953197382279245</v>
+        <v>0.9988461406313796</v>
       </c>
       <c r="O4">
-        <v>1.071634739119942</v>
+        <v>1.100000023842874</v>
       </c>
       <c r="P4">
-        <v>1.058721724243052</v>
+        <v>0.9849793337678201</v>
       </c>
       <c r="Q4">
-        <v>-179.1320733803879</v>
+        <v>34.27420324486579</v>
       </c>
       <c r="R4">
-        <v>63.59656736636623</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>-63.2490901695982</v>
+        <v>146.9280048930568</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9988461406632403</v>
+        <v>0.9988461406634609</v>
       </c>
       <c r="O5">
-        <v>1.100000023842697</v>
+        <v>1.100000023842874</v>
       </c>
       <c r="P5">
-        <v>0.9849793337509865</v>
+        <v>0.9849793337512107</v>
       </c>
       <c r="Q5">
-        <v>34.27420324669393</v>
+        <v>34.27420324666625</v>
       </c>
       <c r="R5">
-        <v>-89.99999999997128</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>146.928004895505</v>
+        <v>146.9280048954822</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>43.10796461343809</v>
+        <v>43.10796461341968</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9.955358137860532</v>
+        <v>9.95535813785628</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3909,43 +3909,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
-        <v>0.6187086059769628</v>
+        <v>0.6187086059765836</v>
       </c>
       <c r="O6">
-        <v>1.100000023842935</v>
+        <v>1.100000023842838</v>
       </c>
       <c r="P6">
-        <v>0.6112532753013482</v>
+        <v>0.6112532753018204</v>
       </c>
       <c r="Q6">
-        <v>63.59656698036181</v>
+        <v>63.59656698025402</v>
       </c>
       <c r="R6">
-        <v>-89.99999999992689</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S6">
-        <v>116.7509101302443</v>
+        <v>116.7509101301737</v>
       </c>
       <c r="T6">
-        <v>43.10796461343809</v>
+        <v>43.10796461341968</v>
       </c>
     </row>
   </sheetData>
@@ -4061,22 +4061,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049986470619764</v>
+        <v>1.049985069482074</v>
       </c>
       <c r="O2">
-        <v>1.049991810360968</v>
+        <v>1.049999952316285</v>
       </c>
       <c r="P2">
-        <v>1.050001353434115</v>
+        <v>1.049994612616487</v>
       </c>
       <c r="Q2">
-        <v>179.9993986945204</v>
+        <v>29.99986757685378</v>
       </c>
       <c r="R2">
-        <v>60.00016822890995</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00046887585556</v>
+        <v>149.999230470721</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4123,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049932313230427</v>
+        <v>1.049922570914869</v>
       </c>
       <c r="O3">
-        <v>1.049956391316272</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="P3">
-        <v>1.050009693913876</v>
+        <v>1.049975875229383</v>
       </c>
       <c r="Q3">
-        <v>179.9966412933059</v>
+        <v>29.99907930920902</v>
       </c>
       <c r="R3">
-        <v>60.00075865369529</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00243784476583</v>
+        <v>149.9958827930337</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4185,22 +4185,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049901251880345</v>
+        <v>1.049898433196768</v>
       </c>
       <c r="O4">
-        <v>1.049947784707017</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="P4">
-        <v>1.050002770727338</v>
+        <v>1.049953421801627</v>
       </c>
       <c r="Q4">
-        <v>179.9965351404839</v>
+        <v>29.99973375089482</v>
       </c>
       <c r="R4">
-        <v>60.00146611638205</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00319830186109</v>
+        <v>149.9950692041297</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>1.04989843319677</v>
       </c>
       <c r="O5">
-        <v>1.049999952316285</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="P5">
-        <v>1.049953421801598</v>
+        <v>1.049953421801599</v>
       </c>
       <c r="Q5">
-        <v>29.99973375089671</v>
+        <v>29.99973375089667</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999632</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S5">
         <v>149.9950692041307</v>
@@ -4273,7 +4273,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03427133653806188</v>
+        <v>0.03427133653806189</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.007914626268232434</v>
+        <v>0.007914626268232437</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4291,43 +4291,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>1.049486215106253</v>
+        <v>1.049486215106252</v>
       </c>
       <c r="O6">
-        <v>1.049999952316285</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P6">
         <v>1.049805445171679</v>
       </c>
       <c r="Q6">
-        <v>29.99607560673486</v>
+        <v>29.99607560673483</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999632</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>149.9737562262302</v>
+        <v>149.9737562262301</v>
       </c>
       <c r="T6">
-        <v>0.03427133653806188</v>
+        <v>0.03427133653806189</v>
       </c>
     </row>
   </sheetData>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.069211965322743</v>
+        <v>1.069211965322762</v>
       </c>
       <c r="G2">
-        <v>149.9640291619602</v>
+        <v>-0.03597083799321052</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.9387871686716606</v>
+        <v>0.9387871686719225</v>
       </c>
       <c r="G3">
-        <v>149.2619585801569</v>
+        <v>-0.7380414197227489</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.8935122209062168</v>
+        <v>0.8935122209065726</v>
       </c>
       <c r="G4">
-        <v>151.2204167668213</v>
+        <v>1.22041676695381</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8935122209216566</v>
+        <v>0.8935122209219969</v>
       </c>
       <c r="G5">
-        <v>1.220416771394491</v>
+        <v>1.220416771520688</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4460,22 +4460,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.40872772417899</v>
+        <v>40.4087277242067</v>
       </c>
       <c r="C6">
-        <v>27.99598821217077</v>
+        <v>27.99598821218996</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451978028</v>
+        <v>0.0007617443451851983</v>
       </c>
       <c r="E6">
-        <v>0.006240294707275743</v>
+        <v>0.006240294707272939</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>83.04041299938353</v>
+        <v>83.04041299949446</v>
       </c>
     </row>
   </sheetData>
@@ -4591,22 +4591,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099985900278217</v>
+        <v>1.099984432643651</v>
       </c>
       <c r="O2">
-        <v>1.099991494457562</v>
+        <v>1.100000023841859</v>
       </c>
       <c r="P2">
-        <v>1.100001491455622</v>
+        <v>1.099994429705891</v>
       </c>
       <c r="Q2">
-        <v>179.9993987250631</v>
+        <v>29.99986759706821</v>
       </c>
       <c r="R2">
-        <v>60.00016823385292</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00046886552755</v>
+        <v>149.9992304963202</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.099929164305092</v>
+        <v>1.099918959299557</v>
       </c>
       <c r="O3">
-        <v>1.099954389967245</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="P3">
-        <v>1.100010228095344</v>
+        <v>1.099974799226226</v>
       </c>
       <c r="Q3">
-        <v>179.9966414552361</v>
+        <v>29.99907942021749</v>
       </c>
       <c r="R3">
-        <v>60.00075868373521</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00243779384952</v>
+        <v>149.9958829249117</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4715,22 +4715,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099896624625497</v>
+        <v>1.099893673067847</v>
       </c>
       <c r="O4">
-        <v>1.099945374029749</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="P4">
-        <v>1.100002975114146</v>
+        <v>1.099951276859666</v>
       </c>
       <c r="Q4">
-        <v>179.996535340285</v>
+        <v>29.9997338726043</v>
       </c>
       <c r="R4">
-        <v>60.00146613818838</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.0031982237839</v>
+        <v>149.9950693821048</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4780,16 +4780,16 @@
         <v>1.099893673067849</v>
       </c>
       <c r="O5">
-        <v>1.100000023841859</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="P5">
-        <v>1.099951276859634</v>
+        <v>1.099951276859635</v>
       </c>
       <c r="Q5">
-        <v>29.99973387260628</v>
+        <v>29.99973387260625</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999631</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S5">
         <v>149.9950693821059</v>
@@ -4812,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.008291303100981471</v>
+        <v>0.008291303100981468</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4821,22 +4821,22 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
         <v>1.099441271427511</v>
@@ -4848,16 +4848,16 @@
         <v>1.099788870684895</v>
       </c>
       <c r="Q6">
-        <v>29.99590204605558</v>
+        <v>29.99590204605552</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999631</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S6">
-        <v>149.9727420935561</v>
+        <v>149.972742093556</v>
       </c>
       <c r="T6">
-        <v>0.03590239504464585</v>
+        <v>0.03590239504464584</v>
       </c>
     </row>
   </sheetData>
@@ -4973,22 +4973,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9287307217077518</v>
+        <v>0.9337495495226288</v>
       </c>
       <c r="O2">
-        <v>0.9443875439593157</v>
+        <v>0.9499999880789027</v>
       </c>
       <c r="P2">
-        <v>0.945067462967593</v>
+        <v>0.9344372090237855</v>
       </c>
       <c r="Q2">
-        <v>179.9518338002812</v>
+        <v>30.52921187619897</v>
       </c>
       <c r="R2">
-        <v>60.54693529636548</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>-60.57020971043283</v>
+        <v>149.3993660191492</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8474755350157351</v>
+        <v>0.8699336534241422</v>
       </c>
       <c r="O3">
-        <v>0.9213724321943099</v>
+        <v>0.9499999880797729</v>
       </c>
       <c r="P3">
-        <v>0.9294784550713203</v>
+        <v>0.8785144284494208</v>
       </c>
       <c r="Q3">
-        <v>179.3835485607545</v>
+        <v>32.47568898724801</v>
       </c>
       <c r="R3">
-        <v>62.62116166804041</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>-62.879635529269</v>
+        <v>146.6553654464857</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8173025129126122</v>
+        <v>0.866569775455961</v>
       </c>
       <c r="O4">
-        <v>0.9317732908814069</v>
+        <v>0.9499999880797729</v>
       </c>
       <c r="P4">
-        <v>0.9052845957106481</v>
+        <v>0.8380226186473128</v>
       </c>
       <c r="Q4">
-        <v>-177.9263579440552</v>
+        <v>35.28843500954328</v>
       </c>
       <c r="R4">
-        <v>64.00539624242563</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>-63.18502654698914</v>
+        <v>147.5713439924642</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8665697754883085</v>
+        <v>0.8665697754894227</v>
       </c>
       <c r="O5">
-        <v>0.9499999880787271</v>
+        <v>0.9499999880797729</v>
       </c>
       <c r="P5">
-        <v>0.8380226186361536</v>
+        <v>0.838022618637125</v>
       </c>
       <c r="Q5">
-        <v>35.28843501116468</v>
+        <v>35.28843501117782</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000858</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>147.5713439951992</v>
+        <v>147.571343995222</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5185,7 +5185,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>36.8648301456474</v>
+        <v>36.86483014565815</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8.51356797014979</v>
+        <v>8.513567970152273</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5203,43 +5203,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.5379595611119803</v>
+        <v>0.5379595611130407</v>
       </c>
       <c r="O6">
-        <v>0.9499999880792939</v>
+        <v>0.9499999880798943</v>
       </c>
       <c r="P6">
-        <v>0.5226663073861413</v>
+        <v>0.5226663073859428</v>
       </c>
       <c r="Q6">
-        <v>64.00539586257335</v>
+        <v>64.0053958626016</v>
       </c>
       <c r="R6">
-        <v>-90.00000000001209</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S6">
-        <v>116.8149737589746</v>
+        <v>116.8149737590455</v>
       </c>
       <c r="T6">
-        <v>36.86483014564739</v>
+        <v>36.86483014565815</v>
       </c>
     </row>
   </sheetData>
@@ -5355,22 +5355,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8798501451399389</v>
+        <v>0.884604824056161</v>
       </c>
       <c r="O2">
-        <v>0.894682923908297</v>
+        <v>0.8999999761579826</v>
       </c>
       <c r="P2">
-        <v>0.8953270576966312</v>
+        <v>0.8852562909429106</v>
       </c>
       <c r="Q2">
-        <v>179.9518338002812</v>
+        <v>30.52921187619897</v>
       </c>
       <c r="R2">
-        <v>60.54693529636548</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>-60.57020971043283</v>
+        <v>149.3993660191492</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8028715482944685</v>
+        <v>0.8241476601742095</v>
       </c>
       <c r="O3">
-        <v>0.8728791341191352</v>
+        <v>0.8999999761588069</v>
       </c>
       <c r="P3">
-        <v>0.8805585241060743</v>
+        <v>0.832276815347974</v>
       </c>
       <c r="Q3">
-        <v>179.3835485607545</v>
+        <v>32.47568898724801</v>
       </c>
       <c r="R3">
-        <v>62.62116166804041</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>-62.87963552926899</v>
+        <v>146.6553654464857</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5479,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7742865803847958</v>
+        <v>0.8209608284593128</v>
       </c>
       <c r="O4">
-        <v>0.8827325790537391</v>
+        <v>0.8999999761588069</v>
       </c>
       <c r="P4">
-        <v>0.8576380260839563</v>
+        <v>0.793916153965035</v>
       </c>
       <c r="Q4">
-        <v>-177.9263579440552</v>
+        <v>35.28843500954327</v>
       </c>
       <c r="R4">
-        <v>64.00539624242562</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>-63.18502654698914</v>
+        <v>147.5713439924641</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8209608284899578</v>
+        <v>0.8209608284910133</v>
       </c>
       <c r="O5">
-        <v>0.8999999761578161</v>
+        <v>0.899999976158807</v>
       </c>
       <c r="P5">
-        <v>0.7939161539544631</v>
+        <v>0.7939161539553834</v>
       </c>
       <c r="Q5">
-        <v>35.28843501116468</v>
+        <v>35.28843501117782</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000858</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>147.5713439951992</v>
+        <v>147.571343995222</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>34.92457544051579</v>
+        <v>34.92457544052598</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8.06548533295117</v>
+        <v>8.065485332953523</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5585,43 +5585,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.5096458928950307</v>
+        <v>0.5096458928960355</v>
       </c>
       <c r="O6">
-        <v>0.8999999761583531</v>
+        <v>0.899999976158922</v>
       </c>
       <c r="P6">
-        <v>0.4951575474620309</v>
+        <v>0.4951575474618429</v>
       </c>
       <c r="Q6">
-        <v>64.00539586257334</v>
+        <v>64.00539586260157</v>
       </c>
       <c r="R6">
-        <v>-90.00000000001209</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S6">
-        <v>116.8149737589746</v>
+        <v>116.8149737590455</v>
       </c>
       <c r="T6">
-        <v>34.92457544051578</v>
+        <v>34.92457544052597</v>
       </c>
     </row>
   </sheetData>
@@ -5737,22 +5737,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499861274926242</v>
+        <v>0.9499846870876113</v>
       </c>
       <c r="O2">
-        <v>0.9499916174166207</v>
+        <v>0.9499999880790703</v>
       </c>
       <c r="P2">
-        <v>0.9500014284608839</v>
+        <v>0.9499944982034473</v>
       </c>
       <c r="Q2">
-        <v>179.99931673623</v>
+        <v>29.99984953624247</v>
       </c>
       <c r="R2">
-        <v>60.00019116724602</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00053279165072</v>
+        <v>149.9991255755829</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5799,22 +5799,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499358655887533</v>
+        <v>0.9499266843571428</v>
       </c>
       <c r="O3">
-        <v>0.9499587464532045</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P3">
-        <v>0.9500091686022482</v>
+        <v>0.9499771082079532</v>
       </c>
       <c r="Q3">
-        <v>179.9964883458269</v>
+        <v>29.99904100574319</v>
       </c>
       <c r="R3">
-        <v>60.00079682289977</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00255247221045</v>
+        <v>149.9956916907817</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5861,22 +5861,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9498956577715058</v>
+        <v>0.9499010146965838</v>
       </c>
       <c r="O4">
-        <v>0.9499531809884816</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P4">
-        <v>0.9499946317120941</v>
+        <v>0.9499424676964715</v>
       </c>
       <c r="Q4">
-        <v>179.9971130697405</v>
+        <v>30.00055977635474</v>
       </c>
       <c r="R4">
-        <v>60.00200312333234</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00344635067252</v>
+        <v>149.9951100660698</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5923,19 +5923,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499010146965899</v>
+        <v>0.9499010146965906</v>
       </c>
       <c r="O5">
-        <v>0.9499999880790705</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P5">
-        <v>0.9499424676964446</v>
+        <v>0.9499424676964453</v>
       </c>
       <c r="Q5">
-        <v>30.00055977635679</v>
+        <v>30.00055977635681</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S5">
         <v>149.9951100660712</v>
@@ -5949,7 +5949,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03100607643367225</v>
+        <v>0.03100607643367227</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.007160546736898374</v>
+        <v>0.007160546736898379</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5967,43 +5967,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9495092789338686</v>
+        <v>0.9495092789338694</v>
       </c>
       <c r="O6">
-        <v>0.9499999880790704</v>
+        <v>0.9499999880790713</v>
       </c>
       <c r="P6">
-        <v>0.9498018431122677</v>
+        <v>0.9498018431122686</v>
       </c>
       <c r="Q6">
-        <v>29.99671799597036</v>
+        <v>29.99671799597038</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S6">
         <v>149.9727237666508</v>
       </c>
       <c r="T6">
-        <v>0.03100607643367224</v>
+        <v>0.03100607643367227</v>
       </c>
     </row>
   </sheetData>
@@ -6119,22 +6119,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999868450764282</v>
+        <v>0.8999854804822245</v>
       </c>
       <c r="O2">
-        <v>0.8999920460569837</v>
+        <v>0.8999999761581413</v>
       </c>
       <c r="P2">
-        <v>0.9000013407303666</v>
+        <v>0.8999947752234132</v>
       </c>
       <c r="Q2">
-        <v>179.99931673623</v>
+        <v>29.99984953624247</v>
       </c>
       <c r="R2">
-        <v>60.00019116724602</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00053279165072</v>
+        <v>149.9991255755829</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6181,22 +6181,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999392285365828</v>
+        <v>0.8999305305278098</v>
       </c>
       <c r="O3">
-        <v>0.8999609051447078</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P3">
-        <v>0.9000086734957674</v>
+        <v>0.8999783004910696</v>
       </c>
       <c r="Q3">
-        <v>179.9964883458269</v>
+        <v>29.99904100574319</v>
       </c>
       <c r="R3">
-        <v>60.00079682289976</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00255247221045</v>
+        <v>149.9956916907817</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6243,22 +6243,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999011369207741</v>
+        <v>0.8999062119023562</v>
       </c>
       <c r="O4">
-        <v>0.8999556325992545</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P4">
-        <v>0.8999949017052873</v>
+        <v>0.8999454831648602</v>
       </c>
       <c r="Q4">
-        <v>179.9971130697405</v>
+        <v>30.00055977635474</v>
       </c>
       <c r="R4">
-        <v>60.00200312333234</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00344635067252</v>
+        <v>149.9951100660698</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6305,19 +6305,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.899906211902362</v>
+        <v>0.8999062119023625</v>
       </c>
       <c r="O5">
-        <v>0.8999999761581415</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P5">
-        <v>0.8999454831648347</v>
+        <v>0.8999454831648352</v>
       </c>
       <c r="Q5">
-        <v>30.00055977635679</v>
+        <v>30.00055977635681</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S5">
         <v>149.9951100660712</v>
@@ -6331,7 +6331,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.02937417726445268</v>
+        <v>0.02937417726445269</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.00678367576142686</v>
+        <v>0.006783675761426863</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6349,43 +6349,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.8995350938165372</v>
+        <v>0.899535093816538</v>
       </c>
       <c r="O6">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761581423</v>
       </c>
       <c r="P6">
-        <v>0.8998122598764193</v>
+        <v>0.8998122598764201</v>
       </c>
       <c r="Q6">
-        <v>29.99671799597037</v>
+        <v>29.99671799597038</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S6">
         <v>149.9727237666508</v>
       </c>
       <c r="T6">
-        <v>0.02937417726445267</v>
+        <v>0.02937417726445269</v>
       </c>
     </row>
   </sheetData>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.03830603642146</v>
+        <v>1.033888420480416</v>
       </c>
       <c r="O2">
-        <v>1.024480804024122</v>
+        <v>1.019485521668202</v>
       </c>
       <c r="P2">
-        <v>1.023965276831615</v>
+        <v>1.033377586531867</v>
       </c>
       <c r="Q2">
-        <v>179.9942102535249</v>
+        <v>29.53443761337991</v>
       </c>
       <c r="R2">
-        <v>59.5137947391577</v>
+        <v>-90.03879109617527</v>
       </c>
       <c r="S2">
-        <v>-59.57441937321749</v>
+        <v>150.4379308241784</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9887044727984711</v>
+        <v>0.9688759041852129</v>
       </c>
       <c r="O3">
-        <v>0.919896028229655</v>
+        <v>0.8902319386663998</v>
       </c>
       <c r="P3">
-        <v>0.9117724066031215</v>
+        <v>0.9611663416916905</v>
       </c>
       <c r="Q3">
-        <v>179.7794399552138</v>
+        <v>27.12738303729492</v>
       </c>
       <c r="R3">
-        <v>56.71511369191054</v>
+        <v>-90.77979689234661</v>
       </c>
       <c r="S3">
-        <v>-57.94883449778596</v>
+        <v>152.1935505044011</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6625,22 +6625,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9716448271865672</v>
+        <v>0.9364896961430428</v>
       </c>
       <c r="O4">
-        <v>0.8730755145066152</v>
+        <v>0.845333943659008</v>
       </c>
       <c r="P4">
-        <v>0.8841211430106873</v>
+        <v>0.9467958029426512</v>
       </c>
       <c r="Q4">
-        <v>-179.514518044967</v>
+        <v>27.3119061746836</v>
       </c>
       <c r="R4">
-        <v>57.46016245574135</v>
+        <v>-88.732799474754</v>
       </c>
       <c r="S4">
-        <v>-55.40375609914942</v>
+        <v>153.9740254310674</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9364896961293313</v>
+        <v>0.9364896961303885</v>
       </c>
       <c r="O5">
-        <v>0.8453339436724913</v>
+        <v>0.8453339436736008</v>
       </c>
       <c r="P5">
-        <v>0.9467958029691408</v>
+        <v>0.9467958029702892</v>
       </c>
       <c r="Q5">
-        <v>27.31190617700673</v>
+        <v>27.31190617707661</v>
       </c>
       <c r="R5">
-        <v>-88.73279947025765</v>
+        <v>-88.73279947018712</v>
       </c>
       <c r="S5">
-        <v>153.9740254328895</v>
+        <v>153.9740254329513</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6716,58 +6716,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>41.36469947761175</v>
+        <v>41.36469947761692</v>
       </c>
       <c r="D6">
-        <v>41.88802071861744</v>
+        <v>41.88802071861998</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.552768293686187</v>
+        <v>9.552768293687377</v>
       </c>
       <c r="G6">
-        <v>9.673624159233992</v>
+        <v>9.67362415923458</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.5609794067177126</v>
+        <v>0.560979406716637</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5609794067177587</v>
+        <v>0.5609794067177442</v>
       </c>
       <c r="Q6">
-        <v>0.4854818366815277</v>
+        <v>0.4854818367582735</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.5145181633161</v>
+        <v>-179.5145181631732</v>
       </c>
       <c r="T6">
-        <v>46.03473022952214</v>
+        <v>46.03473022952723</v>
       </c>
     </row>
   </sheetData>
@@ -6883,22 +6883,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.088266251878227</v>
+        <v>1.083782808395165</v>
       </c>
       <c r="O2">
-        <v>1.074258149459081</v>
+        <v>1.069211965323454</v>
       </c>
       <c r="P2">
-        <v>1.073756250736176</v>
+        <v>1.083285322566815</v>
       </c>
       <c r="Q2">
-        <v>179.9946781636719</v>
+        <v>29.5509230004974</v>
       </c>
       <c r="R2">
-        <v>59.53173547227097</v>
+        <v>-90.03597083799083</v>
       </c>
       <c r="S2">
-        <v>-59.58794303688893</v>
+        <v>150.4235112675343</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6945,22 +6945,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.038494058182523</v>
+        <v>1.018317941922362</v>
       </c>
       <c r="O3">
-        <v>0.9687090122584437</v>
+        <v>0.9387871686737203</v>
       </c>
       <c r="P3">
-        <v>0.9606351160070543</v>
+        <v>1.010640443736718</v>
       </c>
       <c r="Q3">
-        <v>179.7905131912941</v>
+        <v>27.23766864269854</v>
       </c>
       <c r="R3">
-        <v>56.85042106160839</v>
+        <v>-90.73804141972415</v>
       </c>
       <c r="S3">
-        <v>-58.02024160624749</v>
+        <v>152.1170545997395</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.021379690674997</v>
+        <v>0.9856892098040414</v>
       </c>
       <c r="O4">
-        <v>0.9214971657664486</v>
+        <v>0.8935122209084457</v>
       </c>
       <c r="P4">
-        <v>0.9327364810663284</v>
+        <v>0.9962045647962073</v>
       </c>
       <c r="Q4">
-        <v>-179.5350079406338</v>
+        <v>27.41436187780214</v>
       </c>
       <c r="R4">
-        <v>57.56839198610954</v>
+        <v>-88.77958323305887</v>
       </c>
       <c r="S4">
-        <v>-55.58595037886729</v>
+        <v>153.8226837648241</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.985689209789599</v>
+        <v>0.9856892097906811</v>
       </c>
       <c r="O5">
-        <v>0.8935122209226839</v>
+        <v>0.8935122209238702</v>
       </c>
       <c r="P5">
-        <v>0.9962045648241697</v>
+        <v>0.9962045648253828</v>
       </c>
       <c r="Q5">
-        <v>27.41436188013142</v>
+        <v>27.41436188020171</v>
       </c>
       <c r="R5">
-        <v>-88.77958322856408</v>
+        <v>-88.779583228492</v>
       </c>
       <c r="S5">
-        <v>153.8226837666516</v>
+        <v>153.8226837667121</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7098,58 +7098,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>41.67433539577618</v>
+        <v>41.67433539576943</v>
       </c>
       <c r="D6">
-        <v>42.18262870641323</v>
+        <v>42.18262870640377</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.624275647032933</v>
+        <v>9.624275647031373</v>
       </c>
       <c r="G6">
-        <v>9.741660960671544</v>
+        <v>9.741660960669359</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
-        <v>0.5896938437544095</v>
+        <v>0.5896938437540171</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5896938437559787</v>
+        <v>0.5896938437554143</v>
       </c>
       <c r="Q6">
-        <v>0.4649919412540814</v>
+        <v>0.4649919412155878</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.5350080587813</v>
+        <v>-179.5350080587832</v>
       </c>
       <c r="T6">
-        <v>46.19148148391573</v>
+        <v>46.19148148390762</v>
       </c>
     </row>
   </sheetData>
@@ -7265,22 +7265,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049993211303326</v>
+        <v>1.049994611814986</v>
       </c>
       <c r="O2">
-        <v>1.04998787132676</v>
+        <v>1.049979730265621</v>
       </c>
       <c r="P2">
-        <v>1.049978329734111</v>
+        <v>1.04998507028359</v>
       </c>
       <c r="Q2">
-        <v>179.9996993239333</v>
+        <v>29.99923048492417</v>
       </c>
       <c r="R2">
-        <v>59.9989298781506</v>
+        <v>-90.00090188824248</v>
       </c>
       <c r="S2">
-        <v>-60.0004330427601</v>
+        <v>149.9998675626456</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049966131663271</v>
+        <v>1.049975870953186</v>
       </c>
       <c r="O3">
-        <v>1.049942054488679</v>
+        <v>1.049898497017663</v>
       </c>
       <c r="P3">
-        <v>1.049888757009989</v>
+        <v>1.04992257519113</v>
       </c>
       <c r="Q3">
-        <v>179.998320566006</v>
+        <v>29.99588285531672</v>
       </c>
       <c r="R3">
-        <v>59.99420365439553</v>
+        <v>-90.00503781811662</v>
       </c>
       <c r="S3">
-        <v>-60.00259993630995</v>
+        <v>149.9990792468876</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7389,22 +7389,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049950600258693</v>
+        <v>1.049953416632932</v>
       </c>
       <c r="O4">
-        <v>1.049904071386116</v>
+        <v>1.049851907180983</v>
       </c>
       <c r="P4">
-        <v>1.049849090534431</v>
+        <v>1.049898438365347</v>
       </c>
       <c r="Q4">
-        <v>179.9982674888099</v>
+        <v>29.99506933261958</v>
       </c>
       <c r="R4">
-        <v>59.99333700146205</v>
+        <v>-90.00519704499435</v>
       </c>
       <c r="S4">
-        <v>-60.00199858028505</v>
+        <v>149.9997336223455</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7451,19 +7451,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.049953416632902</v>
+        <v>1.049953416632903</v>
       </c>
       <c r="O5">
-        <v>1.049851907180956</v>
+        <v>1.049851907180957</v>
       </c>
       <c r="P5">
         <v>1.049898438365349</v>
       </c>
       <c r="Q5">
-        <v>29.99506933262057</v>
+        <v>29.9950693326206</v>
       </c>
       <c r="R5">
-        <v>-90.00519704499149</v>
+        <v>-90.00519704499146</v>
       </c>
       <c r="S5">
         <v>149.9997336223473</v>
@@ -7492,25 +7492,25 @@
         <v>0.007914647522935411</v>
       </c>
       <c r="G6">
-        <v>0.007914233052659</v>
+        <v>0.007914233052659002</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
         <v>1.049805417804597</v>
@@ -7522,16 +7522,16 @@
         <v>1.049486242470258</v>
       </c>
       <c r="Q6">
-        <v>29.97375674799993</v>
+        <v>29.97375674799998</v>
       </c>
       <c r="R6">
-        <v>-90.03017915474207</v>
+        <v>-90.03017915474202</v>
       </c>
       <c r="S6">
         <v>149.9960750840753</v>
       </c>
       <c r="T6">
-        <v>0.0342729473892761</v>
+        <v>0.03427294738927611</v>
       </c>
     </row>
   </sheetData>
@@ -7647,22 +7647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099992961887486</v>
+        <v>1.099994428866278</v>
       </c>
       <c r="O2">
-        <v>1.099987367461655</v>
+        <v>1.099978839014074</v>
       </c>
       <c r="P2">
-        <v>1.099977372014492</v>
+        <v>1.099984433483281</v>
       </c>
       <c r="Q2">
-        <v>179.9996993392061</v>
+        <v>29.99923051052452</v>
       </c>
       <c r="R2">
-        <v>59.99892991901915</v>
+        <v>-90.00090184243298</v>
       </c>
       <c r="S2">
-        <v>-60.00043300727835</v>
+        <v>149.999867582859</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7709,22 +7709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.099964592910502</v>
+        <v>1.099974794746677</v>
       </c>
       <c r="O3">
-        <v>1.099939368203311</v>
+        <v>1.099893738025533</v>
       </c>
       <c r="P3">
-        <v>1.099883535437526</v>
+        <v>1.099918963779172</v>
       </c>
       <c r="Q3">
-        <v>179.9983206469765</v>
+        <v>29.99588298720121</v>
       </c>
       <c r="R3">
-        <v>59.99420386723094</v>
+        <v>-90.00503757523742</v>
       </c>
       <c r="S3">
-        <v>-60.0025997443502</v>
+        <v>149.9990793578895</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099948322306456</v>
+        <v>1.09995127144522</v>
       </c>
       <c r="O4">
-        <v>1.09989957704482</v>
+        <v>1.099844930798715</v>
       </c>
       <c r="P4">
-        <v>1.099841981374807</v>
+        <v>1.099893678482172</v>
       </c>
       <c r="Q4">
-        <v>179.9982675887161</v>
+        <v>29.99506951059992</v>
       </c>
       <c r="R4">
-        <v>59.99333727932899</v>
+        <v>-90.00519674530969</v>
       </c>
       <c r="S4">
-        <v>-60.00199835868895</v>
+        <v>149.9997337440498</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.099951271445187</v>
+        <v>1.099951271445188</v>
       </c>
       <c r="O5">
         <v>1.099844930798685</v>
       </c>
       <c r="P5">
-        <v>1.099893678482173</v>
+        <v>1.099893678482174</v>
       </c>
       <c r="Q5">
-        <v>29.99506951060096</v>
+        <v>29.99506951060098</v>
       </c>
       <c r="R5">
-        <v>-90.00519674530672</v>
+        <v>-90.00519674530669</v>
       </c>
       <c r="S5">
-        <v>149.9997337440517</v>
+        <v>149.9997337440518</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7877,37 +7877,37 @@
         <v>0.008290891186168155</v>
       </c>
       <c r="H6">
-        <v>0.0005106516136597194</v>
+        <v>0.0005106516136597251</v>
       </c>
       <c r="I6">
-        <v>0.005080919304206397</v>
+        <v>0.005080919304206255</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451849474</v>
+        <v>0.000761744345182562</v>
       </c>
       <c r="K6">
-        <v>0.006240294707282466</v>
+        <v>0.006240294707286588</v>
       </c>
       <c r="L6">
-        <v>0.000761744345198538</v>
+        <v>0.0007617443451985193</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727303</v>
+        <v>0.006240294707272751</v>
       </c>
       <c r="N6">
-        <v>1.099788840909019</v>
+        <v>1.099788840909016</v>
       </c>
       <c r="O6">
-        <v>1.099230173732588</v>
+        <v>1.099230173732585</v>
       </c>
       <c r="P6">
-        <v>1.099441301199902</v>
+        <v>1.099441301199899</v>
       </c>
       <c r="Q6">
-        <v>29.97274263407071</v>
+        <v>29.97274263407073</v>
       </c>
       <c r="R6">
-        <v>-90.03136781435383</v>
+        <v>-90.03136781435381</v>
       </c>
       <c r="S6">
         <v>149.9959015045881</v>
@@ -8029,22 +8029,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9385594223557453</v>
+        <v>0.934572952325905</v>
       </c>
       <c r="O2">
-        <v>0.9254040493665202</v>
+        <v>0.9202097000244793</v>
       </c>
       <c r="P2">
-        <v>0.9242581230872275</v>
+        <v>0.9334382822275619</v>
       </c>
       <c r="Q2">
-        <v>179.9860624010459</v>
+        <v>29.47892351345201</v>
       </c>
       <c r="R2">
-        <v>59.43353348743121</v>
+        <v>-90.09512014424648</v>
       </c>
       <c r="S2">
-        <v>-59.58196850890661</v>
+        <v>150.4538003181771</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8947879314869116</v>
+        <v>0.8785603241857096</v>
       </c>
       <c r="O3">
-        <v>0.834761791217924</v>
+        <v>0.8065751372455071</v>
       </c>
       <c r="P3">
-        <v>0.8242212391851884</v>
+        <v>0.8685514643819039</v>
       </c>
       <c r="Q3">
-        <v>179.7452496021267</v>
+        <v>27.0670343463038</v>
       </c>
       <c r="R3">
-        <v>56.53864844406788</v>
+        <v>-91.056274381061</v>
       </c>
       <c r="S3">
-        <v>-58.18489386169624</v>
+        <v>152.0818356803591</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8153,22 +8153,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8788125464043394</v>
+        <v>0.840745081951469</v>
       </c>
       <c r="O4">
-        <v>0.7824892172502351</v>
+        <v>0.7636659323893639</v>
       </c>
       <c r="P4">
-        <v>0.8053849111972587</v>
+        <v>0.8620949906460387</v>
       </c>
       <c r="Q4">
-        <v>-178.8853210849799</v>
+        <v>28.11130518316999</v>
       </c>
       <c r="R4">
-        <v>58.76295759223839</v>
+        <v>-87.09305266723598</v>
       </c>
       <c r="S4">
-        <v>-54.04661951800593</v>
+        <v>154.8386431601129</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8407450819443704</v>
+        <v>0.8407450819443307</v>
       </c>
       <c r="O5">
-        <v>0.7636659324127987</v>
+        <v>0.7636659324127536</v>
       </c>
       <c r="P5">
-        <v>0.8620949906770716</v>
+        <v>0.862094990677079</v>
       </c>
       <c r="Q5">
-        <v>28.11130518586102</v>
+        <v>28.11130518584049</v>
       </c>
       <c r="R5">
-        <v>-87.09305266248292</v>
+        <v>-87.09305266249898</v>
       </c>
       <c r="S5">
-        <v>154.8386431619109</v>
+        <v>154.8386431618928</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8244,58 +8244,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>35.29455956801005</v>
+        <v>35.29455956802739</v>
       </c>
       <c r="D6">
-        <v>36.327280918241</v>
+        <v>36.32728091825652</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.150929508466268</v>
+        <v>8.150929508470272</v>
       </c>
       <c r="G6">
-        <v>8.389426291841632</v>
+        <v>8.389426291845215</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.5073826640218244</v>
+        <v>0.5073826640216883</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5073826640209037</v>
+        <v>0.5073826640213396</v>
       </c>
       <c r="Q6">
-        <v>1.114678796825117</v>
+        <v>1.114678796834924</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-178.8853212032594</v>
+        <v>-178.8853212032434</v>
       </c>
       <c r="T6">
-        <v>39.63927003696637</v>
+        <v>39.63927003698531</v>
       </c>
     </row>
   </sheetData>
@@ -8351,7 +8351,7 @@
         <v>1.049979730265621</v>
       </c>
       <c r="G2">
-        <v>149.9990981117478</v>
+        <v>-0.0009018882461228145</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.049898497017662</v>
+        <v>1.049898497017663</v>
       </c>
       <c r="G3">
-        <v>149.9949621818736</v>
+        <v>-0.005037818120266376</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8394,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1.049851907180982</v>
+        <v>1.049851907180983</v>
       </c>
       <c r="G4">
-        <v>149.9948029549959</v>
+        <v>-0.005197044997986872</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.049851907180955</v>
+        <v>1.049851907180956</v>
       </c>
       <c r="G5">
-        <v>-0.005197044995163719</v>
+        <v>-0.005197044995118749</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8428,22 +8428,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03426972580693886</v>
+        <v>0.03426972580693888</v>
       </c>
       <c r="C6">
-        <v>0.02374276285742371</v>
+        <v>0.02374276285742373</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100661764</v>
+        <v>0.0007385329100534613</v>
       </c>
       <c r="E6">
-        <v>0.00600934383484958</v>
+        <v>0.006009343834854925</v>
       </c>
       <c r="F6">
         <v>1.049291757515442</v>
       </c>
       <c r="G6">
-        <v>44.99999999999815</v>
+        <v>44.99999999999827</v>
       </c>
     </row>
   </sheetData>
@@ -8559,22 +8559,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8891615456240021</v>
+        <v>0.8853848898589152</v>
       </c>
       <c r="O2">
-        <v>0.8766985608606077</v>
+        <v>0.8717775983946541</v>
       </c>
       <c r="P2">
-        <v>0.8756129465058879</v>
+        <v>0.8843099392544197</v>
       </c>
       <c r="Q2">
-        <v>179.9860624010459</v>
+        <v>29.47892351345201</v>
       </c>
       <c r="R2">
-        <v>59.4335334874312</v>
+        <v>-90.09512014424648</v>
       </c>
       <c r="S2">
-        <v>-59.58196850890661</v>
+        <v>150.4538003181771</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8476938180106439</v>
+        <v>0.8323202955185888</v>
       </c>
       <c r="O3">
-        <v>0.7908269490750014</v>
+        <v>0.7641238035787074</v>
       </c>
       <c r="P3">
-        <v>0.7808411630779535</v>
+        <v>0.8228382179419251</v>
       </c>
       <c r="Q3">
-        <v>179.7452496021266</v>
+        <v>27.0670343463038</v>
       </c>
       <c r="R3">
-        <v>56.53864844406788</v>
+        <v>-91.056274381061</v>
       </c>
       <c r="S3">
-        <v>-58.18489386169624</v>
+        <v>152.0818356803591</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8683,22 +8683,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8325592428802747</v>
+        <v>0.796495329690907</v>
       </c>
       <c r="O4">
-        <v>0.7413055639013324</v>
+        <v>0.7234729784922976</v>
       </c>
       <c r="P4">
-        <v>0.7629962210224042</v>
+        <v>0.8167215586984929</v>
       </c>
       <c r="Q4">
-        <v>-178.8853210849799</v>
+        <v>28.11130518316999</v>
       </c>
       <c r="R4">
-        <v>58.76295759223839</v>
+        <v>-87.09305266723598</v>
       </c>
       <c r="S4">
-        <v>-54.04661951800593</v>
+        <v>154.8386431601129</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7964953296841818</v>
+        <v>0.7964953296841444</v>
       </c>
       <c r="O5">
-        <v>0.723472978514499</v>
+        <v>0.7234729785144564</v>
       </c>
       <c r="P5">
-        <v>0.8167215587278924</v>
+        <v>0.8167215587278993</v>
       </c>
       <c r="Q5">
-        <v>28.11130518586101</v>
+        <v>28.1113051858405</v>
       </c>
       <c r="R5">
-        <v>-87.09305266248292</v>
+        <v>-87.09305266249899</v>
       </c>
       <c r="S5">
-        <v>154.8386431619109</v>
+        <v>154.8386431618928</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8774,58 +8774,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>33.43695070349546</v>
+        <v>33.43695070351188</v>
       </c>
       <c r="D6">
-        <v>34.41531828481011</v>
+        <v>34.41531828482481</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>7.721933110883108</v>
+        <v>7.721933110886901</v>
       </c>
       <c r="G6">
-        <v>7.947877428825307</v>
+        <v>7.947877428828702</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.4806783065819248</v>
+        <v>0.4806783065817959</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.4806783065810526</v>
+        <v>0.4806783065814655</v>
       </c>
       <c r="Q6">
-        <v>1.114678796825161</v>
+        <v>1.114678796834825</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-178.8853212032594</v>
+        <v>-178.8853212032435</v>
       </c>
       <c r="T6">
-        <v>37.55299214301309</v>
+        <v>37.55299214303103</v>
       </c>
     </row>
   </sheetData>
@@ -8941,22 +8941,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499930575310989</v>
+        <v>0.9499944973623559</v>
       </c>
       <c r="O2">
-        <v>0.9499875676144007</v>
+        <v>0.9499791979636318</v>
       </c>
       <c r="P2">
-        <v>0.9499777581091863</v>
+        <v>0.9499846879286976</v>
       </c>
       <c r="Q2">
-        <v>179.9996583413131</v>
+        <v>29.99912560043202</v>
       </c>
       <c r="R2">
-        <v>59.99878402126421</v>
+        <v>-90.00102481525582</v>
       </c>
       <c r="S2">
-        <v>-60.00049206601801</v>
+        <v>149.9998495113865</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9003,22 +9003,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499679253606668</v>
+        <v>0.949977104040357</v>
       </c>
       <c r="O3">
-        <v>0.9499450465922317</v>
+        <v>0.9499038087630122</v>
       </c>
       <c r="P3">
-        <v>0.9498946293750816</v>
+        <v>0.9499266885246513</v>
       </c>
       <c r="Q3">
-        <v>179.9982440870331</v>
+        <v>29.99569179806629</v>
       </c>
       <c r="R3">
-        <v>59.99393613280436</v>
+        <v>-90.00526722363975</v>
       </c>
       <c r="S3">
-        <v>-60.00271474699595</v>
+        <v>149.9990408984096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9065,22 +9065,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499478203621737</v>
+        <v>0.9499424631441236</v>
       </c>
       <c r="O4">
-        <v>0.9498903042541739</v>
+        <v>0.9498435003064293</v>
       </c>
       <c r="P4">
-        <v>0.9498488580826374</v>
+        <v>0.949901019248389</v>
       </c>
       <c r="Q4">
-        <v>179.9985564556007</v>
+        <v>29.99511030230252</v>
       </c>
       <c r="R4">
-        <v>59.99366687757819</v>
+        <v>-90.00433015760096</v>
       </c>
       <c r="S4">
-        <v>-60.0008836484072</v>
+        <v>150.0005595400492</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9127,19 +9127,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499424631440971</v>
+        <v>0.9499424631440972</v>
       </c>
       <c r="O5">
         <v>0.9498435003064096</v>
       </c>
       <c r="P5">
-        <v>0.9499010192483955</v>
+        <v>0.9499010192483957</v>
       </c>
       <c r="Q5">
-        <v>29.99511030230397</v>
+        <v>29.99511030230391</v>
       </c>
       <c r="R5">
-        <v>-90.00433015759744</v>
+        <v>-90.00433015759749</v>
       </c>
       <c r="S5">
         <v>150.0005595400513</v>
@@ -9156,52 +9156,52 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03100590168653194</v>
+        <v>0.03100590168653196</v>
       </c>
       <c r="D6">
-        <v>0.0310045488189441</v>
+        <v>0.03100454881894412</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.007160506380774374</v>
+        <v>0.007160506380774379</v>
       </c>
       <c r="G6">
-        <v>0.007160193949383312</v>
+        <v>0.007160193949383315</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9498018170268172</v>
+        <v>0.949801817026817</v>
       </c>
       <c r="O6">
-        <v>0.9493111849763776</v>
+        <v>0.9493111849763773</v>
       </c>
       <c r="P6">
-        <v>0.9495093050130278</v>
+        <v>0.9495093050130275</v>
       </c>
       <c r="Q6">
-        <v>29.97272463900339</v>
+        <v>29.97272463900336</v>
       </c>
       <c r="R6">
-        <v>-90.03057029446013</v>
+        <v>-90.03057029446015</v>
       </c>
       <c r="S6">
         <v>149.9967171225022</v>
@@ -9323,22 +9323,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999934103759442</v>
+        <v>0.8999947744265897</v>
       </c>
       <c r="O2">
-        <v>0.8999882094023026</v>
+        <v>0.8999802802595794</v>
       </c>
       <c r="P2">
-        <v>0.8999789161869659</v>
+        <v>0.8999854812790431</v>
       </c>
       <c r="Q2">
-        <v>179.9996583413131</v>
+        <v>29.99912560043202</v>
       </c>
       <c r="R2">
-        <v>59.9987840212642</v>
+        <v>-90.00102481525582</v>
       </c>
       <c r="S2">
-        <v>-60.00049206601801</v>
+        <v>149.9998495113865</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9385,22 +9385,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999696009516562</v>
+        <v>0.8999782965428204</v>
       </c>
       <c r="O3">
-        <v>0.8999479263292304</v>
+        <v>0.8999088589126198</v>
       </c>
       <c r="P3">
-        <v>0.8999001626504911</v>
+        <v>0.8999305344759758</v>
       </c>
       <c r="Q3">
-        <v>179.9982440870331</v>
+        <v>29.99569179806629</v>
       </c>
       <c r="R3">
-        <v>59.99393613280436</v>
+        <v>-90.00526722363975</v>
       </c>
       <c r="S3">
-        <v>-60.00271474699595</v>
+        <v>149.9990408984096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9447,22 +9447,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999505541112445</v>
+        <v>0.8999454788521096</v>
       </c>
       <c r="O4">
-        <v>0.8998960651675828</v>
+        <v>0.8998517245861275</v>
       </c>
       <c r="P4">
-        <v>0.8998568003740434</v>
+        <v>0.8999062162145925</v>
       </c>
       <c r="Q4">
-        <v>179.9985564556007</v>
+        <v>29.99511030230252</v>
       </c>
       <c r="R4">
-        <v>59.99366687757819</v>
+        <v>-90.00433015760096</v>
       </c>
       <c r="S4">
-        <v>-60.0008836484072</v>
+        <v>150.0005595400492</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999454788520845</v>
+        <v>0.8999454788520846</v>
       </c>
       <c r="O5">
         <v>0.8998517245861087</v>
@@ -9518,10 +9518,10 @@
         <v>0.8999062162145989</v>
       </c>
       <c r="Q5">
-        <v>29.99511030230397</v>
+        <v>29.99511030230391</v>
       </c>
       <c r="R5">
-        <v>-90.00433015759744</v>
+        <v>-90.00433015759749</v>
       </c>
       <c r="S5">
         <v>150.0005595400513</v>
@@ -9538,58 +9538,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.02937401171453259</v>
+        <v>0.02937401171453261</v>
       </c>
       <c r="D6">
-        <v>0.02937273005051986</v>
+        <v>0.02937273005051988</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.006783637529309919</v>
+        <v>0.006783637529309924</v>
       </c>
       <c r="G6">
-        <v>0.006783341541680406</v>
+        <v>0.00678334154168041</v>
       </c>
       <c r="H6">
-        <v>0.0005120000251343793</v>
+        <v>0.0005120000251343859</v>
       </c>
       <c r="I6">
-        <v>0.005094335828683501</v>
+        <v>0.00509433582868336</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479346787</v>
+        <v>0.0009575007479249351</v>
       </c>
       <c r="K6">
-        <v>0.006296894770917619</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479203481</v>
+        <v>0.0009575007479203282</v>
       </c>
       <c r="M6">
-        <v>0.006296894770919861</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.8998122351638875</v>
+        <v>0.8998122351638873</v>
       </c>
       <c r="O6">
-        <v>0.8993474258594252</v>
+        <v>0.8993474258594251</v>
       </c>
       <c r="P6">
-        <v>0.8995351185231086</v>
+        <v>0.8995351185231084</v>
       </c>
       <c r="Q6">
-        <v>29.97272463900338</v>
+        <v>29.97272463900336</v>
       </c>
       <c r="R6">
-        <v>-90.03057029446013</v>
+        <v>-90.03057029446015</v>
       </c>
       <c r="S6">
         <v>149.9967171225022</v>
       </c>
       <c r="T6">
-        <v>0.02937579031850676</v>
+        <v>0.02937579031850678</v>
       </c>
     </row>
   </sheetData>
@@ -9645,7 +9645,7 @@
         <v>1.099978839014074</v>
       </c>
       <c r="G2">
-        <v>149.9990981575573</v>
+        <v>-0.0009018424366363302</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.099893738025532</v>
+        <v>1.099893738025533</v>
       </c>
       <c r="G3">
-        <v>149.9949624247528</v>
+        <v>-0.005037575241080463</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9688,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1.099844930798714</v>
+        <v>1.099844930798715</v>
       </c>
       <c r="G4">
-        <v>149.9948032546806</v>
+        <v>-0.005196745313343392</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.099844930798684</v>
+        <v>1.099844930798685</v>
       </c>
       <c r="G5">
-        <v>-0.00519674531038368</v>
+        <v>-0.005196745310338735</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9722,22 +9722,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03590070767517213</v>
+        <v>0.03590070767517219</v>
       </c>
       <c r="C6">
-        <v>0.02487274025906314</v>
+        <v>0.02487274025906318</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451978028</v>
+        <v>0.0007617443451851983</v>
       </c>
       <c r="E6">
-        <v>0.006240294707275743</v>
+        <v>0.006240294707272939</v>
       </c>
       <c r="F6">
-        <v>1.099230173732585</v>
+        <v>1.099230173732587</v>
       </c>
       <c r="G6">
-        <v>44.99999999999814</v>
+        <v>44.99999999999825</v>
       </c>
     </row>
   </sheetData>
@@ -9790,10 +9790,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9202097000238783</v>
+        <v>0.9202097000230514</v>
       </c>
       <c r="G2">
-        <v>149.9048798557205</v>
+        <v>-0.09512014424988395</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8065751372452601</v>
+        <v>0.8065751372444899</v>
       </c>
       <c r="G3">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063374</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9836,10 +9836,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7636659323891967</v>
+        <v>0.7636659323883896</v>
       </c>
       <c r="G4">
-        <v>152.9069473327529</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9859,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7636659324126011</v>
+        <v>0.7636659324117794</v>
       </c>
       <c r="G5">
-        <v>2.906947337496182</v>
+        <v>2.906947337501109</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9870,22 +9870,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>34.44552616790283</v>
+        <v>34.44552616794237</v>
       </c>
       <c r="C6">
-        <v>23.86456092211006</v>
+        <v>23.86456092213745</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242143</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926767</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>81.3538824332835</v>
+        <v>81.35388243329812</v>
       </c>
     </row>
   </sheetData>
@@ -9938,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8717775983940845</v>
+        <v>0.8717775983933012</v>
       </c>
       <c r="G2">
-        <v>149.9048798557205</v>
+        <v>-0.09512014424988403</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9961,10 +9961,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.7641238035784736</v>
+        <v>0.764123803577744</v>
       </c>
       <c r="G3">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063374</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9984,10 +9984,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7234729784921393</v>
+        <v>0.7234729784913747</v>
       </c>
       <c r="G4">
-        <v>152.9069473327529</v>
+        <v>2.906947332764126</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10007,10 +10007,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7234729785143119</v>
+        <v>0.7234729785135333</v>
       </c>
       <c r="G5">
-        <v>2.906947337496182</v>
+        <v>2.906947337501109</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10018,22 +10018,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>32.63260328302965</v>
+        <v>32.63260328306709</v>
       </c>
       <c r="C6">
-        <v>22.60853108467188</v>
+        <v>22.60853108469782</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242143</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926767</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>81.3538824332835</v>
+        <v>81.35388243329812</v>
       </c>
     </row>
   </sheetData>
@@ -10086,10 +10086,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9499791979636301</v>
+        <v>0.9499791979636297</v>
       </c>
       <c r="G2">
-        <v>149.9989751847345</v>
+        <v>-0.001024815259467745</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.9499038087630102</v>
+        <v>0.9499038087630096</v>
       </c>
       <c r="G3">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389589</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10132,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.9498435003064272</v>
+        <v>0.9498435003064266</v>
       </c>
       <c r="G4">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604896</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.9498435003064076</v>
+        <v>0.9498435003064071</v>
       </c>
       <c r="G5">
-        <v>-0.004330157601162779</v>
+        <v>-0.004330157601146444</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10166,19 +10166,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03100437393278748</v>
+        <v>0.03100437393278751</v>
       </c>
       <c r="C6">
-        <v>0.0214804606834646</v>
+        <v>0.02148046068346462</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242143</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926767</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
-        <v>0.9493111849763747</v>
+        <v>0.9493111849763752</v>
       </c>
       <c r="G6">
         <v>44.99999999999817</v>
@@ -10234,10 +10234,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8999802802595779</v>
+        <v>0.8999802802595775</v>
       </c>
       <c r="G2">
-        <v>149.9989751847345</v>
+        <v>-0.001024815259467745</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8999088589126178</v>
+        <v>0.8999088589126175</v>
       </c>
       <c r="G3">
-        <v>149.9947327763505</v>
+        <v>-0.00526722364338959</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10280,10 +10280,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.8998517245861254</v>
+        <v>0.8998517245861249</v>
       </c>
       <c r="G4">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604898</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8998517245861068</v>
+        <v>0.8998517245861064</v>
       </c>
       <c r="G5">
-        <v>-0.004330157601162776</v>
+        <v>-0.004330157601146445</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10314,19 +10314,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.02937256436890011</v>
+        <v>0.02937256436890014</v>
       </c>
       <c r="C6">
-        <v>0.02034990983744619</v>
+        <v>0.02034990983744621</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242143</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926767</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
-        <v>0.8993474258594228</v>
+        <v>0.8993474258594233</v>
       </c>
       <c r="G6">
         <v>44.99999999999816</v>
@@ -10442,22 +10442,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952315168</v>
+        <v>1.042756082098258</v>
       </c>
       <c r="O2">
-        <v>1.02750457968155</v>
+        <v>1.01948552166781</v>
       </c>
       <c r="P2">
-        <v>1.026893559235467</v>
+        <v>1.04215400372766</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999575</v>
+        <v>29.26447752701105</v>
       </c>
       <c r="R2">
-        <v>59.23431352170109</v>
+        <v>-90.03879109617672</v>
       </c>
       <c r="S2">
-        <v>-59.2916295621355</v>
+        <v>150.7169722376508</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -10501,22 +10501,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952313864</v>
+        <v>1.017850815583789</v>
       </c>
       <c r="O3">
-        <v>0.9386302707469873</v>
+        <v>0.8902319386658908</v>
       </c>
       <c r="P3">
-        <v>0.9268184944722071</v>
+        <v>1.006968728073372</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999163</v>
+        <v>25.92977054716383</v>
       </c>
       <c r="R3">
-        <v>55.21460949020871</v>
+        <v>-90.77979689235561</v>
       </c>
       <c r="S3">
-        <v>-56.28012863118837</v>
+        <v>153.7687858259493</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -10560,22 +10560,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952313864</v>
+        <v>0.9942448483047938</v>
       </c>
       <c r="O4">
-        <v>0.8913852178485501</v>
+        <v>0.8453339436584718</v>
       </c>
       <c r="P4">
-        <v>0.910256314331353</v>
+        <v>1.011198185106088</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999163</v>
+        <v>25.15127081992804</v>
       </c>
       <c r="R4">
-        <v>55.19339620985289</v>
+        <v>-88.73279947476489</v>
       </c>
       <c r="S4">
-        <v>-53.51967073513292</v>
+        <v>155.2989288465904</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9942448482759485</v>
+        <v>0.9942448482769434</v>
       </c>
       <c r="O5">
-        <v>0.8453339436721427</v>
+        <v>0.8453339436730644</v>
       </c>
       <c r="P5">
-        <v>1.011198185138582</v>
+        <v>1.011198185139571</v>
       </c>
       <c r="Q5">
-        <v>25.15127082102004</v>
+        <v>25.15127082109856</v>
       </c>
       <c r="R5">
-        <v>-88.73279947027228</v>
+        <v>-88.73279947019802</v>
       </c>
       <c r="S5">
-        <v>155.2989288469815</v>
+        <v>155.2989288470546</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10645,55 +10645,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.68462518855983</v>
+        <v>34.68462518857614</v>
       </c>
       <c r="D6">
-        <v>34.68462518855983</v>
+        <v>34.68462518857614</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.010071195101878</v>
+        <v>8.010071195105644</v>
       </c>
       <c r="G6">
-        <v>8.010071195101878</v>
+        <v>8.010071195105644</v>
       </c>
       <c r="H6">
-        <v>0.0004874401766207747</v>
+        <v>0.0004874401766207814</v>
       </c>
       <c r="I6">
-        <v>0.00484996842675795</v>
+        <v>0.004849968426757815</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100625364</v>
+        <v>0.0007385329100564497</v>
       </c>
       <c r="K6">
-        <v>0.006009343834861058</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100691376</v>
+        <v>0.0007385329100691168</v>
       </c>
       <c r="M6">
-        <v>0.006009343834855013</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.9093266326761349</v>
+        <v>0.9093266326765918</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9093266326763536</v>
+        <v>0.9093266326768066</v>
       </c>
       <c r="Q6">
-        <v>-8.703467235478532E-11</v>
+        <v>-4.867876620728455E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999177</v>
+        <v>-179.9999999999892</v>
       </c>
     </row>
   </sheetData>
